--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -1,135 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70879F08-BA64-0E4B-B0A3-77AB2D1FFE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Rifle_session_started_at_17-33_" sheetId="2" r:id="rId2"/>
-    <sheet name="Rifle_session_started_at_17-36_" sheetId="3" r:id="rId3"/>
-    <sheet name="Rifle_session_started_at_17-42_" sheetId="4" r:id="rId4"/>
-    <sheet name="Rifle_session_started_at_17-52_" sheetId="5" r:id="rId5"/>
-    <sheet name="Rifle_session_started_at_17-55_" sheetId="6" r:id="rId6"/>
+    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Rifle_session_started_at_17-33_" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Rifle_session_started_at_17-36_" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Rifle_session_started_at_17-42_" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Rifle_session_started_at_17-52_" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Rifle_session_started_at_17-55_" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="71">
-  <si>
-    <t>File</t>
-  </si>
-  <si>
-    <t>Date</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="59">
+  <si>
+    <t>Row</t>
   </si>
   <si>
     <t>Shots</t>
   </si>
   <si>
-    <t>Avg Speed</t>
+    <t>V0 Avg</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>Lowest</t>
+  </si>
+  <si>
+    <t>Spread</t>
   </si>
   <si>
     <t>Std Dev</t>
   </si>
   <si>
-    <t>Spread</t>
-  </si>
-  <si>
-    <t>Speed Sum</t>
-  </si>
-  <si>
-    <t>Rifle_session_started_at_17-33_2026-03-20_17-33-48.csv</t>
-  </si>
-  <si>
-    <t>March 20, 2026 at 5:33 PM</t>
-  </si>
-  <si>
-    <t>Rifle_session_started_at_17-36_2026-03-20_17-36-09.csv</t>
-  </si>
-  <si>
-    <t>March 20, 2026 at 5:36 PM</t>
-  </si>
-  <si>
-    <t>Rifle_session_started_at_17-42_2026-03-20_17-42-40.csv</t>
-  </si>
-  <si>
-    <t>March 20, 2026 at 5:42 PM</t>
-  </si>
-  <si>
-    <t>Rifle_session_started_at_17-52_2026-03-20_17-52-06.csv</t>
-  </si>
-  <si>
-    <t>March 20, 2026 at 5:52 PM</t>
-  </si>
-  <si>
-    <t>Rifle_session_started_at_17-55_2026-03-20_17-55-15.csv</t>
-  </si>
-  <si>
-    <t>March 20, 2026 at 5:55 PM</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
+    <t>#</t>
+  </si>
+  <si>
+    <t>SPEED (FPS)</t>
+  </si>
+  <si>
+    <t>Δ AVG (FPS)</t>
+  </si>
+  <si>
+    <t>KE (FT-LB)</t>
+  </si>
+  <si>
+    <t>POWER FACTOR (KGR⋅FT/S)</t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>CLEAN BORE</t>
+  </si>
+  <si>
+    <t>COLD BORE</t>
+  </si>
+  <si>
+    <t>SHOT NOTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:34:06 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:34:40 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:35:04 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:35:23 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:35:38 PM</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>OVERALL AVG</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>SPEED (FPS)</t>
-  </si>
-  <si>
-    <t>Δ AVG (FPS)</t>
-  </si>
-  <si>
-    <t>KE (FT-LB)</t>
-  </si>
-  <si>
-    <t>POWER FACTOR (KGR⋅FT/S)</t>
-  </si>
-  <si>
-    <t>TIME</t>
-  </si>
-  <si>
-    <t>CLEAN BORE</t>
-  </si>
-  <si>
-    <t>COLD BORE</t>
-  </si>
-  <si>
-    <t>SHOT NOTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5:34:06 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5:34:40 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5:35:04 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5:35:23 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5:35:38 PM</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>AVERAGE SPEED</t>
   </si>
   <si>
@@ -163,7 +123,7 @@
     <t>All shots included in the calculations</t>
   </si>
   <si>
-    <t>﻿</t>
+    <t xml:space="preserve">﻿</t>
   </si>
   <si>
     <t xml:space="preserve"> 5:32:40 PM</t>
@@ -238,27 +198,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -281,14 +231,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,247 +581,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="10" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2491</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2487.5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2484.6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2526.3</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2517.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2504.3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2509.6</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2512.8</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2545.9</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2534.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2473.3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2466.3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2462.4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2506.4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2499.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="E6" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>2491</v>
-      </c>
-      <c r="E2">
+      <c r="B7" s="1">
         <v>11.9</v>
       </c>
-      <c r="F2">
-        <v>31</v>
-      </c>
-      <c r="G2">
-        <v>12455.100000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2487.5</v>
-      </c>
-      <c r="E3">
+      <c r="C7" s="1">
         <v>20.2</v>
       </c>
-      <c r="F3">
-        <v>43.3</v>
-      </c>
-      <c r="G3">
-        <v>9950.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>2484.6</v>
-      </c>
-      <c r="E4">
+      <c r="D7" s="1">
         <v>18.5</v>
       </c>
-      <c r="F4">
-        <v>50.4</v>
-      </c>
-      <c r="G4">
-        <v>12422.800000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>2526.3000000000002</v>
-      </c>
-      <c r="E5">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="F5">
-        <v>39.5</v>
-      </c>
-      <c r="G5">
-        <v>12631.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>2517.1999999999998</v>
-      </c>
-      <c r="E6">
+      <c r="E7" s="1">
+        <v>16.4</v>
+      </c>
+      <c r="F7" s="1">
         <v>14.4</v>
-      </c>
-      <c r="F6">
-        <v>34.9</v>
-      </c>
-      <c r="G6">
-        <v>12585.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2">
-        <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2">
-        <v>60045.400000000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2501.8916666666669</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -878,88 +783,88 @@
         <v>-4</v>
       </c>
       <c r="D2">
-        <v>2444.1999999999998</v>
+        <v>2444.2</v>
       </c>
       <c r="E2">
         <v>442.7</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2504.3000000000002</v>
+        <v>2504.3</v>
       </c>
       <c r="C3">
         <v>13.3</v>
       </c>
       <c r="D3">
-        <v>2478.3000000000002</v>
+        <v>2478.3</v>
       </c>
       <c r="E3">
         <v>445.8</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2504.3000000000002</v>
+        <v>2504.3</v>
       </c>
       <c r="C4">
         <v>13.3</v>
       </c>
       <c r="D4">
-        <v>2478.3000000000002</v>
+        <v>2478.3</v>
       </c>
       <c r="E4">
         <v>445.8</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2473.3000000000002</v>
+        <v>2473.3</v>
       </c>
       <c r="C5">
         <v>-17.7</v>
@@ -971,392 +876,392 @@
         <v>440.3</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2486.1999999999998</v>
+        <v>2486.2</v>
       </c>
       <c r="C6">
         <v>-4.8</v>
       </c>
       <c r="D6">
-        <v>2442.6999999999998</v>
+        <v>2442.7</v>
       </c>
       <c r="E6">
         <v>442.5</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>2491</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>11.9</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>443.4</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>2452.1999999999998</v>
+        <v>2452.2</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1367,25 +1272,25 @@
         <v>22.1</v>
       </c>
       <c r="D2">
-        <v>2488.8000000000002</v>
+        <v>2488.8</v>
       </c>
       <c r="E2">
         <v>446.7</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1393,459 +1298,459 @@
         <v>2468.4</v>
       </c>
       <c r="C3">
-        <v>-19.100000000000001</v>
+        <v>-19.1</v>
       </c>
       <c r="D3">
-        <v>2407.8000000000002</v>
+        <v>2407.8</v>
       </c>
       <c r="E3">
         <v>439.4</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2505.8000000000002</v>
+        <v>2505.8</v>
       </c>
       <c r="C4">
         <v>18.3</v>
       </c>
       <c r="D4">
-        <v>2481.3000000000002</v>
+        <v>2481.3</v>
       </c>
       <c r="E4">
         <v>446</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2466.3000000000002</v>
+        <v>2466.3</v>
       </c>
       <c r="C5">
         <v>-21.2</v>
       </c>
       <c r="D5">
-        <v>2403.8000000000002</v>
+        <v>2403.8</v>
       </c>
       <c r="E5">
         <v>439</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>2487.5</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>20.2</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>43.3</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>442.8</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>2445.4</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2512.8000000000002</v>
+        <v>2512.8</v>
       </c>
       <c r="C2">
         <v>28.3</v>
       </c>
       <c r="D2">
-        <v>2495.1999999999998</v>
+        <v>2495.2</v>
       </c>
       <c r="E2">
         <v>447.3</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1853,28 +1758,28 @@
         <v>2493.9</v>
       </c>
       <c r="C3">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="D3">
-        <v>2457.6999999999998</v>
+        <v>2457.7</v>
       </c>
       <c r="E3">
         <v>443.9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1885,30 +1790,30 @@
         <v>-18.2</v>
       </c>
       <c r="D4">
-        <v>2403.8000000000002</v>
+        <v>2403.8</v>
       </c>
       <c r="E4">
         <v>439</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2487.3000000000002</v>
+        <v>2487.3</v>
       </c>
       <c r="C5">
         <v>2.8</v>
@@ -1920,19 +1825,19 @@
         <v>442.7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1949,363 +1854,363 @@
         <v>438.3</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>2484.6</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>18.5</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>50.4</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>442.3</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>2439.6</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2322,19 +2227,19 @@
         <v>451.8</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2345,25 +2250,25 @@
         <v>7.1</v>
       </c>
       <c r="D3">
-        <v>2536.3000000000002</v>
+        <v>2536.3</v>
       </c>
       <c r="E3">
         <v>451</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2371,7 +2276,7 @@
         <v>2506.4</v>
       </c>
       <c r="C4">
-        <v>-19.899999999999999</v>
+        <v>-19.9</v>
       </c>
       <c r="D4">
         <v>2482.5</v>
@@ -2380,19 +2285,19 @@
         <v>446.1</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2400,409 +2305,409 @@
         <v>2545.9</v>
       </c>
       <c r="C5">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="D5">
-        <v>2561.3000000000002</v>
+        <v>2561.3</v>
       </c>
       <c r="E5">
         <v>453.2</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2507.3000000000002</v>
+        <v>2507.3</v>
       </c>
       <c r="C6">
         <v>-19</v>
       </c>
       <c r="D6">
-        <v>2484.3000000000002</v>
+        <v>2484.3</v>
       </c>
       <c r="E6">
         <v>446.3</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>2526.3000000000002</v>
+        <v>2526.3</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>16.399999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>39.5</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>449.7</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>2522.1999999999998</v>
+        <v>2522.2</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2534.8000000000002</v>
+        <v>2534.8</v>
       </c>
       <c r="C2">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="D2">
         <v>2539.1</v>
@@ -2811,19 +2716,19 @@
         <v>451.2</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2831,7 +2736,7 @@
         <v>2500.6</v>
       </c>
       <c r="C3">
-        <v>-16.600000000000001</v>
+        <v>-16.6</v>
       </c>
       <c r="D3">
         <v>2471.1</v>
@@ -2840,19 +2745,19 @@
         <v>445.1</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2869,19 +2774,19 @@
         <v>449</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2892,25 +2797,25 @@
         <v>-17.3</v>
       </c>
       <c r="D5">
-        <v>2469.6999999999998</v>
+        <v>2469.7</v>
       </c>
       <c r="E5">
         <v>445</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2927,321 +2832,321 @@
         <v>450</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>2517.1999999999998</v>
+        <v>2517.2</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>14.4</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>34.9</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>448.1</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>2504</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>